--- a/templates/card_template.xlsx
+++ b/templates/card_template.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="стр.1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="стр.2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Лицевая сторона" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Оборотная сторона" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -82,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -110,6 +110,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -481,17 +484,17 @@
   <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -816,24 +819,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="H1" s="4" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Оборотная сторона личной карточки</t>
         </is>
@@ -847,7 +849,7 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Модель, марка, артикул, класс защиты СИЗ</t>
+          <t>Модель, марка, артикул, класс защиты СИЗ, дерматологических СИЗ</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -858,15 +860,14 @@
       <c r="D3" s="8" t="n"/>
       <c r="E3" s="8" t="n"/>
       <c r="F3" s="8" t="n"/>
-      <c r="G3" s="8" t="n"/>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Возвращено</t>
         </is>
       </c>
+      <c r="H3" s="8" t="n"/>
       <c r="I3" s="8" t="n"/>
       <c r="J3" s="8" t="n"/>
-      <c r="K3" s="8" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n"/>
@@ -883,8 +884,8 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Лично/
-дозатор</t>
+          <t>Лично /
+карточка</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -894,27 +895,22 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>подпись выдавшего</t>
+          <t>дата</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>дата</t>
+          <t>количество</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>количество</t>
+          <t>подпись сдавшего СИЗ</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>подпись сдавшего СИЗ</t>
-        </is>
-      </c>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t>Акт списания (дата, номер)</t>
+          <t>Акт списания, дата и номер</t>
         </is>
       </c>
     </row>
@@ -949,279 +945,196 @@
       <c r="J5" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="K5" s="8" t="n">
-        <v>11</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n"/>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="11" t="n"/>
-      <c r="K6" s="11" t="n"/>
+      <c r="A6" s="12" t="n"/>
+      <c r="B6" s="12" t="n"/>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="12" t="n"/>
+      <c r="J6" s="12" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="n"/>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="11" t="n"/>
-      <c r="J7" s="11" t="n"/>
-      <c r="K7" s="11" t="n"/>
+      <c r="A7" s="12" t="n"/>
+      <c r="B7" s="12" t="n"/>
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="n"/>
+      <c r="H7" s="12" t="n"/>
+      <c r="I7" s="12" t="n"/>
+      <c r="J7" s="12" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="11" t="n"/>
-      <c r="J8" s="11" t="n"/>
-      <c r="K8" s="11" t="n"/>
+      <c r="A8" s="12" t="n"/>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="12" t="n"/>
+      <c r="G8" s="12" t="n"/>
+      <c r="H8" s="12" t="n"/>
+      <c r="I8" s="12" t="n"/>
+      <c r="J8" s="12" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="n"/>
-      <c r="J9" s="11" t="n"/>
-      <c r="K9" s="11" t="n"/>
+      <c r="A9" s="12" t="n"/>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n"/>
-      <c r="I10" s="11" t="n"/>
-      <c r="J10" s="11" t="n"/>
-      <c r="K10" s="11" t="n"/>
+      <c r="A10" s="12" t="n"/>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="12" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="11" t="n"/>
-      <c r="J11" s="11" t="n"/>
-      <c r="K11" s="11" t="n"/>
+      <c r="A11" s="12" t="n"/>
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="12" t="n"/>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="12" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="n"/>
-      <c r="J12" s="11" t="n"/>
-      <c r="K12" s="11" t="n"/>
+      <c r="A12" s="12" t="n"/>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
+      <c r="H12" s="12" t="n"/>
+      <c r="I12" s="12" t="n"/>
+      <c r="J12" s="12" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="n"/>
-      <c r="J13" s="11" t="n"/>
-      <c r="K13" s="11" t="n"/>
+      <c r="A13" s="12" t="n"/>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="12" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="n"/>
-      <c r="I14" s="11" t="n"/>
-      <c r="J14" s="11" t="n"/>
-      <c r="K14" s="11" t="n"/>
+      <c r="A14" s="12" t="n"/>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
+      <c r="H14" s="12" t="n"/>
+      <c r="I14" s="12" t="n"/>
+      <c r="J14" s="12" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="11" t="n"/>
+      <c r="A15" s="12" t="n"/>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="12" t="n"/>
+      <c r="I15" s="12" t="n"/>
+      <c r="J15" s="12" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="11" t="n"/>
-      <c r="I16" s="11" t="n"/>
-      <c r="J16" s="11" t="n"/>
-      <c r="K16" s="11" t="n"/>
+      <c r="A16" s="12" t="n"/>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n"/>
-      <c r="I17" s="11" t="n"/>
-      <c r="J17" s="11" t="n"/>
-      <c r="K17" s="11" t="n"/>
+      <c r="A17" s="12" t="n"/>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="11" t="n"/>
-      <c r="J18" s="11" t="n"/>
-      <c r="K18" s="11" t="n"/>
+      <c r="A18" s="12" t="n"/>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="12" t="n"/>
+      <c r="J18" s="12" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="n"/>
-      <c r="I19" s="11" t="n"/>
-      <c r="J19" s="11" t="n"/>
-      <c r="K19" s="11" t="n"/>
+      <c r="A19" s="12" t="n"/>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="11" t="n"/>
-      <c r="I20" s="11" t="n"/>
-      <c r="J20" s="11" t="n"/>
-      <c r="K20" s="11" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
-      <c r="J21" s="11" t="n"/>
-      <c r="K21" s="11" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
-      <c r="H22" s="11" t="n"/>
-      <c r="I22" s="11" t="n"/>
-      <c r="J22" s="11" t="n"/>
-      <c r="K22" s="11" t="n"/>
+      <c r="A20" s="12" t="n"/>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="12" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="n"/>
-      <c r="I23" s="11" t="n"/>
-      <c r="J23" s="11" t="n"/>
-      <c r="K23" s="11" t="n"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>* информация указывается только для дерматологических СИЗ</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
-      <c r="H24" s="11" t="n"/>
-      <c r="I24" s="11" t="n"/>
-      <c r="J24" s="11" t="n"/>
-      <c r="K24" s="11" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="11" t="n"/>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="11" t="n"/>
-      <c r="I25" s="11" t="n"/>
-      <c r="J25" s="11" t="n"/>
-      <c r="K25" s="11" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>* информация указывается только для дерматологических СИЗ</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>** информация указывается для всех СИЗ, кроме дерматологических СИЗ и СИЗ однократного применения</t>
         </is>
@@ -1229,11 +1142,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="H1:K1"/>
-    <mergeCell ref="C3:G3"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/templates/card_template.xlsx
+++ b/templates/card_template.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Лицевая сторона" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Оборотная сторона" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лицевая сторона" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборотная сторона" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Лицевая сторона'!$A$1:$DD$37</definedName>
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -523,6 +523,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2119,12 +2124,8 @@
       <c r="AS29" s="110" t="n"/>
       <c r="AT29" s="110" t="n"/>
       <c r="AU29" s="110" t="n"/>
-      <c r="AV29" s="111" t="n"/>
-      <c r="AW29" s="86" t="inlineStr">
-        <is>
-          <t>Пункт Норм</t>
-        </is>
-      </c>
+      <c r="AV29" s="110" t="n"/>
+      <c r="AW29" s="110" t="n"/>
       <c r="AX29" s="110" t="n"/>
       <c r="AY29" s="110" t="n"/>
       <c r="AZ29" s="110" t="n"/>
@@ -2134,20 +2135,19 @@
       <c r="BD29" s="110" t="n"/>
       <c r="BE29" s="110" t="n"/>
       <c r="BF29" s="110" t="n"/>
-      <c r="BG29" s="110" t="n"/>
-      <c r="BH29" s="110" t="n"/>
+      <c r="BG29" s="111" t="n"/>
+      <c r="BH29" s="86" t="inlineStr">
+        <is>
+          <t>Пункт Норм</t>
+        </is>
+      </c>
       <c r="BI29" s="110" t="n"/>
       <c r="BJ29" s="110" t="n"/>
       <c r="BK29" s="110" t="n"/>
       <c r="BL29" s="110" t="n"/>
       <c r="BM29" s="110" t="n"/>
-      <c r="BN29" s="111" t="n"/>
-      <c r="BO29" s="86" t="inlineStr">
-        <is>
-          <t>Единица
-измерения, периодичность выдачи</t>
-        </is>
-      </c>
+      <c r="BN29" s="110" t="n"/>
+      <c r="BO29" s="110" t="n"/>
       <c r="BP29" s="110" t="n"/>
       <c r="BQ29" s="110" t="n"/>
       <c r="BR29" s="110" t="n"/>
@@ -2162,18 +2162,18 @@
       <c r="CA29" s="110" t="n"/>
       <c r="CB29" s="110" t="n"/>
       <c r="CC29" s="110" t="n"/>
-      <c r="CD29" s="110" t="n"/>
-      <c r="CE29" s="110" t="n"/>
+      <c r="CD29" s="111" t="n"/>
+      <c r="CE29" s="86" t="inlineStr">
+        <is>
+          <t>Единица
+измерения, периодичность выдачи</t>
+        </is>
+      </c>
       <c r="CF29" s="110" t="n"/>
       <c r="CG29" s="110" t="n"/>
       <c r="CH29" s="110" t="n"/>
-      <c r="CI29" s="111" t="n"/>
-      <c r="CJ29" s="86" t="inlineStr">
-        <is>
-          <t>Количество
-на период</t>
-        </is>
-      </c>
+      <c r="CI29" s="110" t="n"/>
+      <c r="CJ29" s="110" t="n"/>
       <c r="CK29" s="110" t="n"/>
       <c r="CL29" s="110" t="n"/>
       <c r="CM29" s="110" t="n"/>
@@ -2183,8 +2183,13 @@
       <c r="CQ29" s="110" t="n"/>
       <c r="CR29" s="110" t="n"/>
       <c r="CS29" s="110" t="n"/>
-      <c r="CT29" s="110" t="n"/>
-      <c r="CU29" s="110" t="n"/>
+      <c r="CT29" s="111" t="n"/>
+      <c r="CU29" s="86" t="inlineStr">
+        <is>
+          <t>Количество
+на период</t>
+        </is>
+      </c>
       <c r="CV29" s="110" t="n"/>
       <c r="CW29" s="110" t="n"/>
       <c r="CX29" s="110" t="n"/>
@@ -2243,8 +2248,8 @@
       <c r="AS30" s="110" t="n"/>
       <c r="AT30" s="110" t="n"/>
       <c r="AU30" s="110" t="n"/>
-      <c r="AV30" s="111" t="n"/>
-      <c r="AW30" s="89" t="n"/>
+      <c r="AV30" s="110" t="n"/>
+      <c r="AW30" s="110" t="n"/>
       <c r="AX30" s="110" t="n"/>
       <c r="AY30" s="110" t="n"/>
       <c r="AZ30" s="110" t="n"/>
@@ -2254,15 +2259,15 @@
       <c r="BD30" s="110" t="n"/>
       <c r="BE30" s="110" t="n"/>
       <c r="BF30" s="110" t="n"/>
-      <c r="BG30" s="110" t="n"/>
-      <c r="BH30" s="110" t="n"/>
+      <c r="BG30" s="111" t="n"/>
+      <c r="BH30" s="89" t="n"/>
       <c r="BI30" s="110" t="n"/>
       <c r="BJ30" s="110" t="n"/>
       <c r="BK30" s="110" t="n"/>
       <c r="BL30" s="110" t="n"/>
       <c r="BM30" s="110" t="n"/>
-      <c r="BN30" s="111" t="n"/>
-      <c r="BO30" s="90" t="n"/>
+      <c r="BN30" s="110" t="n"/>
+      <c r="BO30" s="110" t="n"/>
       <c r="BP30" s="110" t="n"/>
       <c r="BQ30" s="110" t="n"/>
       <c r="BR30" s="110" t="n"/>
@@ -2277,13 +2282,13 @@
       <c r="CA30" s="110" t="n"/>
       <c r="CB30" s="110" t="n"/>
       <c r="CC30" s="110" t="n"/>
-      <c r="CD30" s="110" t="n"/>
-      <c r="CE30" s="110" t="n"/>
+      <c r="CD30" s="111" t="n"/>
+      <c r="CE30" s="90" t="n"/>
       <c r="CF30" s="110" t="n"/>
       <c r="CG30" s="110" t="n"/>
       <c r="CH30" s="110" t="n"/>
-      <c r="CI30" s="111" t="n"/>
-      <c r="CJ30" s="90" t="n"/>
+      <c r="CI30" s="110" t="n"/>
+      <c r="CJ30" s="110" t="n"/>
       <c r="CK30" s="110" t="n"/>
       <c r="CL30" s="110" t="n"/>
       <c r="CM30" s="110" t="n"/>
@@ -2293,8 +2298,8 @@
       <c r="CQ30" s="110" t="n"/>
       <c r="CR30" s="110" t="n"/>
       <c r="CS30" s="110" t="n"/>
-      <c r="CT30" s="110" t="n"/>
-      <c r="CU30" s="110" t="n"/>
+      <c r="CT30" s="111" t="n"/>
+      <c r="CU30" s="90" t="n"/>
       <c r="CV30" s="110" t="n"/>
       <c r="CW30" s="110" t="n"/>
       <c r="CX30" s="110" t="n"/>
@@ -2353,8 +2358,8 @@
       <c r="AS31" s="110" t="n"/>
       <c r="AT31" s="110" t="n"/>
       <c r="AU31" s="110" t="n"/>
-      <c r="AV31" s="111" t="n"/>
-      <c r="AW31" s="89" t="n"/>
+      <c r="AV31" s="110" t="n"/>
+      <c r="AW31" s="110" t="n"/>
       <c r="AX31" s="110" t="n"/>
       <c r="AY31" s="110" t="n"/>
       <c r="AZ31" s="110" t="n"/>
@@ -2364,15 +2369,15 @@
       <c r="BD31" s="110" t="n"/>
       <c r="BE31" s="110" t="n"/>
       <c r="BF31" s="110" t="n"/>
-      <c r="BG31" s="110" t="n"/>
-      <c r="BH31" s="110" t="n"/>
+      <c r="BG31" s="111" t="n"/>
+      <c r="BH31" s="89" t="n"/>
       <c r="BI31" s="110" t="n"/>
       <c r="BJ31" s="110" t="n"/>
       <c r="BK31" s="110" t="n"/>
       <c r="BL31" s="110" t="n"/>
       <c r="BM31" s="110" t="n"/>
-      <c r="BN31" s="111" t="n"/>
-      <c r="BO31" s="90" t="n"/>
+      <c r="BN31" s="110" t="n"/>
+      <c r="BO31" s="110" t="n"/>
       <c r="BP31" s="110" t="n"/>
       <c r="BQ31" s="110" t="n"/>
       <c r="BR31" s="110" t="n"/>
@@ -2387,13 +2392,13 @@
       <c r="CA31" s="110" t="n"/>
       <c r="CB31" s="110" t="n"/>
       <c r="CC31" s="110" t="n"/>
-      <c r="CD31" s="110" t="n"/>
-      <c r="CE31" s="110" t="n"/>
+      <c r="CD31" s="111" t="n"/>
+      <c r="CE31" s="90" t="n"/>
       <c r="CF31" s="110" t="n"/>
       <c r="CG31" s="110" t="n"/>
       <c r="CH31" s="110" t="n"/>
-      <c r="CI31" s="111" t="n"/>
-      <c r="CJ31" s="90" t="n"/>
+      <c r="CI31" s="110" t="n"/>
+      <c r="CJ31" s="110" t="n"/>
       <c r="CK31" s="110" t="n"/>
       <c r="CL31" s="110" t="n"/>
       <c r="CM31" s="110" t="n"/>
@@ -2403,8 +2408,8 @@
       <c r="CQ31" s="110" t="n"/>
       <c r="CR31" s="110" t="n"/>
       <c r="CS31" s="110" t="n"/>
-      <c r="CT31" s="110" t="n"/>
-      <c r="CU31" s="110" t="n"/>
+      <c r="CT31" s="111" t="n"/>
+      <c r="CU31" s="90" t="n"/>
       <c r="CV31" s="110" t="n"/>
       <c r="CW31" s="110" t="n"/>
       <c r="CX31" s="110" t="n"/>
@@ -2463,8 +2468,8 @@
       <c r="AS32" s="110" t="n"/>
       <c r="AT32" s="110" t="n"/>
       <c r="AU32" s="110" t="n"/>
-      <c r="AV32" s="111" t="n"/>
-      <c r="AW32" s="89" t="n"/>
+      <c r="AV32" s="110" t="n"/>
+      <c r="AW32" s="110" t="n"/>
       <c r="AX32" s="110" t="n"/>
       <c r="AY32" s="110" t="n"/>
       <c r="AZ32" s="110" t="n"/>
@@ -2474,15 +2479,15 @@
       <c r="BD32" s="110" t="n"/>
       <c r="BE32" s="110" t="n"/>
       <c r="BF32" s="110" t="n"/>
-      <c r="BG32" s="110" t="n"/>
-      <c r="BH32" s="110" t="n"/>
+      <c r="BG32" s="111" t="n"/>
+      <c r="BH32" s="89" t="n"/>
       <c r="BI32" s="110" t="n"/>
       <c r="BJ32" s="110" t="n"/>
       <c r="BK32" s="110" t="n"/>
       <c r="BL32" s="110" t="n"/>
       <c r="BM32" s="110" t="n"/>
-      <c r="BN32" s="111" t="n"/>
-      <c r="BO32" s="90" t="n"/>
+      <c r="BN32" s="110" t="n"/>
+      <c r="BO32" s="110" t="n"/>
       <c r="BP32" s="110" t="n"/>
       <c r="BQ32" s="110" t="n"/>
       <c r="BR32" s="110" t="n"/>
@@ -2497,13 +2502,13 @@
       <c r="CA32" s="110" t="n"/>
       <c r="CB32" s="110" t="n"/>
       <c r="CC32" s="110" t="n"/>
-      <c r="CD32" s="110" t="n"/>
-      <c r="CE32" s="110" t="n"/>
+      <c r="CD32" s="111" t="n"/>
+      <c r="CE32" s="90" t="n"/>
       <c r="CF32" s="110" t="n"/>
       <c r="CG32" s="110" t="n"/>
       <c r="CH32" s="110" t="n"/>
-      <c r="CI32" s="111" t="n"/>
-      <c r="CJ32" s="90" t="n"/>
+      <c r="CI32" s="110" t="n"/>
+      <c r="CJ32" s="110" t="n"/>
       <c r="CK32" s="110" t="n"/>
       <c r="CL32" s="110" t="n"/>
       <c r="CM32" s="110" t="n"/>
@@ -2513,8 +2518,8 @@
       <c r="CQ32" s="110" t="n"/>
       <c r="CR32" s="110" t="n"/>
       <c r="CS32" s="110" t="n"/>
-      <c r="CT32" s="110" t="n"/>
-      <c r="CU32" s="110" t="n"/>
+      <c r="CT32" s="111" t="n"/>
+      <c r="CU32" s="90" t="n"/>
       <c r="CV32" s="110" t="n"/>
       <c r="CW32" s="110" t="n"/>
       <c r="CX32" s="110" t="n"/>
@@ -2573,8 +2578,8 @@
       <c r="AS33" s="110" t="n"/>
       <c r="AT33" s="110" t="n"/>
       <c r="AU33" s="110" t="n"/>
-      <c r="AV33" s="111" t="n"/>
-      <c r="AW33" s="89" t="n"/>
+      <c r="AV33" s="110" t="n"/>
+      <c r="AW33" s="110" t="n"/>
       <c r="AX33" s="110" t="n"/>
       <c r="AY33" s="110" t="n"/>
       <c r="AZ33" s="110" t="n"/>
@@ -2584,15 +2589,15 @@
       <c r="BD33" s="110" t="n"/>
       <c r="BE33" s="110" t="n"/>
       <c r="BF33" s="110" t="n"/>
-      <c r="BG33" s="110" t="n"/>
-      <c r="BH33" s="110" t="n"/>
+      <c r="BG33" s="111" t="n"/>
+      <c r="BH33" s="89" t="n"/>
       <c r="BI33" s="110" t="n"/>
       <c r="BJ33" s="110" t="n"/>
       <c r="BK33" s="110" t="n"/>
       <c r="BL33" s="110" t="n"/>
       <c r="BM33" s="110" t="n"/>
-      <c r="BN33" s="111" t="n"/>
-      <c r="BO33" s="90" t="n"/>
+      <c r="BN33" s="110" t="n"/>
+      <c r="BO33" s="110" t="n"/>
       <c r="BP33" s="110" t="n"/>
       <c r="BQ33" s="110" t="n"/>
       <c r="BR33" s="110" t="n"/>
@@ -2607,13 +2612,13 @@
       <c r="CA33" s="110" t="n"/>
       <c r="CB33" s="110" t="n"/>
       <c r="CC33" s="110" t="n"/>
-      <c r="CD33" s="110" t="n"/>
-      <c r="CE33" s="110" t="n"/>
+      <c r="CD33" s="111" t="n"/>
+      <c r="CE33" s="90" t="n"/>
       <c r="CF33" s="110" t="n"/>
       <c r="CG33" s="110" t="n"/>
       <c r="CH33" s="110" t="n"/>
-      <c r="CI33" s="111" t="n"/>
-      <c r="CJ33" s="90" t="n"/>
+      <c r="CI33" s="110" t="n"/>
+      <c r="CJ33" s="110" t="n"/>
       <c r="CK33" s="110" t="n"/>
       <c r="CL33" s="110" t="n"/>
       <c r="CM33" s="110" t="n"/>
@@ -2623,8 +2628,8 @@
       <c r="CQ33" s="110" t="n"/>
       <c r="CR33" s="110" t="n"/>
       <c r="CS33" s="110" t="n"/>
-      <c r="CT33" s="110" t="n"/>
-      <c r="CU33" s="110" t="n"/>
+      <c r="CT33" s="111" t="n"/>
+      <c r="CU33" s="90" t="n"/>
       <c r="CV33" s="110" t="n"/>
       <c r="CW33" s="110" t="n"/>
       <c r="CX33" s="110" t="n"/>
@@ -2838,62 +2843,62 @@
     <mergeCell ref="AW37:BN37"/>
     <mergeCell ref="AE24:BM24"/>
     <mergeCell ref="BX20:DD20"/>
-    <mergeCell ref="BO30:CI30"/>
     <mergeCell ref="CA22:DD22"/>
     <mergeCell ref="BO16:BT16"/>
     <mergeCell ref="T21:BM21"/>
+    <mergeCell ref="BH30:CD30"/>
     <mergeCell ref="L19:BM19"/>
-    <mergeCell ref="CJ29:DD29"/>
+    <mergeCell ref="A29:BG29"/>
+    <mergeCell ref="CE31:CT31"/>
     <mergeCell ref="CB27:DD27"/>
     <mergeCell ref="BS2:DD8"/>
-    <mergeCell ref="AW33:BN33"/>
-    <mergeCell ref="BO32:CI32"/>
     <mergeCell ref="BR25:CA25"/>
-    <mergeCell ref="AW30:BN30"/>
-    <mergeCell ref="CJ31:DD31"/>
+    <mergeCell ref="A31:BG31"/>
+    <mergeCell ref="BH32:CD32"/>
     <mergeCell ref="BR36:CU36"/>
+    <mergeCell ref="A30:BG30"/>
+    <mergeCell ref="CU33:DD33"/>
     <mergeCell ref="CB25:DD25"/>
-    <mergeCell ref="AW29:BN29"/>
     <mergeCell ref="AE22:BM22"/>
     <mergeCell ref="BR37:CU37"/>
+    <mergeCell ref="CE32:CT32"/>
     <mergeCell ref="V20:AU20"/>
     <mergeCell ref="A20:F20"/>
+    <mergeCell ref="CU30:DD30"/>
     <mergeCell ref="BW19:DD19"/>
-    <mergeCell ref="BO33:CI33"/>
     <mergeCell ref="G20:U20"/>
-    <mergeCell ref="CJ30:DD30"/>
-    <mergeCell ref="A33:AV33"/>
+    <mergeCell ref="BH31:CD31"/>
+    <mergeCell ref="CU29:DD29"/>
     <mergeCell ref="A22:AD22"/>
-    <mergeCell ref="AW31:BN31"/>
+    <mergeCell ref="BH33:CD33"/>
     <mergeCell ref="AF16:BN16"/>
     <mergeCell ref="BR23:BX23"/>
-    <mergeCell ref="A32:AV32"/>
     <mergeCell ref="AV20:BM20"/>
+    <mergeCell ref="CU32:DD32"/>
     <mergeCell ref="BS1:DD1"/>
-    <mergeCell ref="BO29:CI29"/>
     <mergeCell ref="BR24:CI24"/>
     <mergeCell ref="BY23:DD23"/>
-    <mergeCell ref="A29:AV29"/>
-    <mergeCell ref="CJ32:DD32"/>
+    <mergeCell ref="CU31:DD31"/>
     <mergeCell ref="AW36:BN36"/>
     <mergeCell ref="A12:DD12"/>
+    <mergeCell ref="BH29:CD29"/>
+    <mergeCell ref="CE30:CT30"/>
     <mergeCell ref="BR19:BV19"/>
     <mergeCell ref="A23:Z23"/>
     <mergeCell ref="A27:BM27"/>
-    <mergeCell ref="BO31:CI31"/>
     <mergeCell ref="BR20:BW20"/>
     <mergeCell ref="AA23:BM23"/>
-    <mergeCell ref="A31:AV31"/>
+    <mergeCell ref="CE33:CT33"/>
+    <mergeCell ref="CE29:CT29"/>
     <mergeCell ref="BR27:CA27"/>
     <mergeCell ref="A19:K19"/>
     <mergeCell ref="A24:AD24"/>
     <mergeCell ref="A21:S21"/>
-    <mergeCell ref="A30:AV30"/>
+    <mergeCell ref="A33:BG33"/>
     <mergeCell ref="A17:DD17"/>
-    <mergeCell ref="AW32:BN32"/>
+    <mergeCell ref="A32:BG32"/>
     <mergeCell ref="CJ24:DD24"/>
     <mergeCell ref="BR22:BZ22"/>
-    <mergeCell ref="CJ33:DD33"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.3149606299212598" top="0.5905511811023623" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2949,20 +2954,20 @@
       <c r="N3" s="109" t="n"/>
       <c r="O3" s="109" t="n"/>
       <c r="P3" s="109" t="n"/>
-      <c r="Q3" s="112" t="n"/>
-      <c r="R3" s="86" t="inlineStr">
-        <is>
-          <t>Модель, марка, артикул, класс защиты СИЗ, дерматологи-ческих СИЗ</t>
-        </is>
-      </c>
+      <c r="Q3" s="109" t="n"/>
+      <c r="R3" s="109" t="n"/>
       <c r="S3" s="109" t="n"/>
       <c r="T3" s="109" t="n"/>
       <c r="U3" s="109" t="n"/>
       <c r="V3" s="109" t="n"/>
       <c r="W3" s="109" t="n"/>
       <c r="X3" s="109" t="n"/>
-      <c r="Y3" s="109" t="n"/>
-      <c r="Z3" s="109" t="n"/>
+      <c r="Y3" s="112" t="n"/>
+      <c r="Z3" s="86" t="inlineStr">
+        <is>
+          <t>Модель, марка, артикул, класс защиты СИЗ, дерматологических СИЗ</t>
+        </is>
+      </c>
       <c r="AA3" s="109" t="n"/>
       <c r="AB3" s="109" t="n"/>
       <c r="AC3" s="109" t="n"/>
@@ -2971,20 +2976,20 @@
       <c r="AF3" s="109" t="n"/>
       <c r="AG3" s="109" t="n"/>
       <c r="AH3" s="109" t="n"/>
-      <c r="AI3" s="112" t="n"/>
-      <c r="AJ3" s="86" t="inlineStr">
+      <c r="AI3" s="109" t="n"/>
+      <c r="AJ3" s="109" t="n"/>
+      <c r="AK3" s="109" t="n"/>
+      <c r="AL3" s="109" t="n"/>
+      <c r="AM3" s="109" t="n"/>
+      <c r="AN3" s="109" t="n"/>
+      <c r="AO3" s="109" t="n"/>
+      <c r="AP3" s="109" t="n"/>
+      <c r="AQ3" s="112" t="n"/>
+      <c r="AR3" s="86" t="inlineStr">
         <is>
           <t>Выдано</t>
         </is>
       </c>
-      <c r="AK3" s="110" t="n"/>
-      <c r="AL3" s="110" t="n"/>
-      <c r="AM3" s="110" t="n"/>
-      <c r="AN3" s="110" t="n"/>
-      <c r="AO3" s="110" t="n"/>
-      <c r="AP3" s="110" t="n"/>
-      <c r="AQ3" s="110" t="n"/>
-      <c r="AR3" s="110" t="n"/>
       <c r="AS3" s="110" t="n"/>
       <c r="AT3" s="110" t="n"/>
       <c r="AU3" s="110" t="n"/>
@@ -3071,16 +3076,16 @@
       <c r="N4" s="108" t="n"/>
       <c r="O4" s="108" t="n"/>
       <c r="P4" s="108" t="n"/>
-      <c r="Q4" s="114" t="n"/>
-      <c r="R4" s="113" t="n"/>
+      <c r="Q4" s="108" t="n"/>
+      <c r="R4" s="108" t="n"/>
       <c r="S4" s="108" t="n"/>
       <c r="T4" s="108" t="n"/>
       <c r="U4" s="108" t="n"/>
       <c r="V4" s="108" t="n"/>
       <c r="W4" s="108" t="n"/>
       <c r="X4" s="108" t="n"/>
-      <c r="Y4" s="108" t="n"/>
-      <c r="Z4" s="108" t="n"/>
+      <c r="Y4" s="114" t="n"/>
+      <c r="Z4" s="113" t="n"/>
       <c r="AA4" s="108" t="n"/>
       <c r="AB4" s="108" t="n"/>
       <c r="AC4" s="108" t="n"/>
@@ -3089,25 +3094,21 @@
       <c r="AF4" s="108" t="n"/>
       <c r="AG4" s="108" t="n"/>
       <c r="AH4" s="108" t="n"/>
-      <c r="AI4" s="114" t="n"/>
-      <c r="AJ4" s="86" t="inlineStr">
+      <c r="AI4" s="108" t="n"/>
+      <c r="AJ4" s="108" t="n"/>
+      <c r="AK4" s="108" t="n"/>
+      <c r="AL4" s="108" t="n"/>
+      <c r="AM4" s="108" t="n"/>
+      <c r="AN4" s="108" t="n"/>
+      <c r="AO4" s="108" t="n"/>
+      <c r="AP4" s="108" t="n"/>
+      <c r="AQ4" s="114" t="n"/>
+      <c r="AR4" s="86" t="inlineStr">
         <is>
           <t>дата</t>
         </is>
       </c>
-      <c r="AK4" s="110" t="n"/>
-      <c r="AL4" s="110" t="n"/>
-      <c r="AM4" s="110" t="n"/>
-      <c r="AN4" s="110" t="n"/>
-      <c r="AO4" s="110" t="n"/>
-      <c r="AP4" s="110" t="n"/>
-      <c r="AQ4" s="110" t="n"/>
-      <c r="AR4" s="111" t="n"/>
-      <c r="AS4" s="86" t="inlineStr">
-        <is>
-          <t>коли-чество</t>
-        </is>
-      </c>
+      <c r="AS4" s="110" t="n"/>
       <c r="AT4" s="110" t="n"/>
       <c r="AU4" s="110" t="n"/>
       <c r="AV4" s="110" t="n"/>
@@ -3117,8 +3118,7 @@
       <c r="AZ4" s="111" t="n"/>
       <c r="BA4" s="86" t="inlineStr">
         <is>
-          <t>Лично/
-доза-тор *</t>
+          <t>количество</t>
         </is>
       </c>
       <c r="BB4" s="110" t="n"/>
@@ -3130,7 +3130,7 @@
       <c r="BH4" s="111" t="n"/>
       <c r="BI4" s="86" t="inlineStr">
         <is>
-          <t>подпись получив-шего СИЗ</t>
+          <t>подпись получившего СИЗ</t>
         </is>
       </c>
       <c r="BJ4" s="110" t="n"/>
@@ -3157,7 +3157,7 @@
       <c r="CA4" s="111" t="n"/>
       <c r="CB4" s="86" t="inlineStr">
         <is>
-          <t>коли-чество</t>
+          <t>количество</t>
         </is>
       </c>
       <c r="CC4" s="110" t="n"/>
@@ -3169,7 +3169,7 @@
       <c r="CI4" s="111" t="n"/>
       <c r="CJ4" s="86" t="inlineStr">
         <is>
-          <t>подпись сдавше-го СИЗ</t>
+          <t>подпись сдавшего СИЗ</t>
         </is>
       </c>
       <c r="CK4" s="110" t="n"/>
@@ -3216,18 +3216,18 @@
       <c r="N5" s="110" t="n"/>
       <c r="O5" s="110" t="n"/>
       <c r="P5" s="110" t="n"/>
-      <c r="Q5" s="111" t="n"/>
-      <c r="R5" s="100" t="n">
-        <v>2</v>
-      </c>
+      <c r="Q5" s="110" t="n"/>
+      <c r="R5" s="110" t="n"/>
       <c r="S5" s="110" t="n"/>
       <c r="T5" s="110" t="n"/>
       <c r="U5" s="110" t="n"/>
       <c r="V5" s="110" t="n"/>
       <c r="W5" s="110" t="n"/>
       <c r="X5" s="110" t="n"/>
-      <c r="Y5" s="110" t="n"/>
-      <c r="Z5" s="110" t="n"/>
+      <c r="Y5" s="111" t="n"/>
+      <c r="Z5" s="100" t="n">
+        <v>2</v>
+      </c>
       <c r="AA5" s="110" t="n"/>
       <c r="AB5" s="110" t="n"/>
       <c r="AC5" s="110" t="n"/>
@@ -3236,21 +3236,19 @@
       <c r="AF5" s="110" t="n"/>
       <c r="AG5" s="110" t="n"/>
       <c r="AH5" s="110" t="n"/>
-      <c r="AI5" s="111" t="n"/>
-      <c r="AJ5" s="100" t="n">
-        <v>3</v>
-      </c>
+      <c r="AI5" s="110" t="n"/>
+      <c r="AJ5" s="110" t="n"/>
       <c r="AK5" s="110" t="n"/>
       <c r="AL5" s="110" t="n"/>
       <c r="AM5" s="110" t="n"/>
       <c r="AN5" s="110" t="n"/>
       <c r="AO5" s="110" t="n"/>
       <c r="AP5" s="110" t="n"/>
-      <c r="AQ5" s="110" t="n"/>
-      <c r="AR5" s="111" t="n"/>
-      <c r="AS5" s="100" t="n">
-        <v>4</v>
-      </c>
+      <c r="AQ5" s="111" t="n"/>
+      <c r="AR5" s="100" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS5" s="110" t="n"/>
       <c r="AT5" s="110" t="n"/>
       <c r="AU5" s="110" t="n"/>
       <c r="AV5" s="110" t="n"/>
@@ -3259,7 +3257,7 @@
       <c r="AY5" s="110" t="n"/>
       <c r="AZ5" s="111" t="n"/>
       <c r="BA5" s="100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB5" s="110" t="n"/>
       <c r="BC5" s="110" t="n"/>
@@ -3269,7 +3267,7 @@
       <c r="BG5" s="110" t="n"/>
       <c r="BH5" s="111" t="n"/>
       <c r="BI5" s="100" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BJ5" s="110" t="n"/>
       <c r="BK5" s="110" t="n"/>
@@ -3281,7 +3279,7 @@
       <c r="BQ5" s="110" t="n"/>
       <c r="BR5" s="111" t="n"/>
       <c r="BS5" s="100" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BT5" s="110" t="n"/>
       <c r="BU5" s="110" t="n"/>
@@ -3292,7 +3290,7 @@
       <c r="BZ5" s="110" t="n"/>
       <c r="CA5" s="111" t="n"/>
       <c r="CB5" s="100" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CC5" s="110" t="n"/>
       <c r="CD5" s="110" t="n"/>
@@ -3302,7 +3300,7 @@
       <c r="CH5" s="110" t="n"/>
       <c r="CI5" s="111" t="n"/>
       <c r="CJ5" s="100" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CK5" s="110" t="n"/>
       <c r="CL5" s="110" t="n"/>
@@ -3314,7 +3312,7 @@
       <c r="CR5" s="110" t="n"/>
       <c r="CS5" s="111" t="n"/>
       <c r="CT5" s="100" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CU5" s="110" t="n"/>
       <c r="CV5" s="110" t="n"/>
@@ -3329,50 +3327,50 @@
     </row>
     <row r="6" ht="24" customFormat="1" customHeight="1" s="21">
       <c r="A6" s="101" t="n"/>
-      <c r="B6" s="110" t="n"/>
-      <c r="C6" s="110" t="n"/>
-      <c r="D6" s="110" t="n"/>
-      <c r="E6" s="110" t="n"/>
-      <c r="F6" s="110" t="n"/>
-      <c r="G6" s="110" t="n"/>
-      <c r="H6" s="110" t="n"/>
-      <c r="I6" s="110" t="n"/>
-      <c r="J6" s="110" t="n"/>
-      <c r="K6" s="110" t="n"/>
-      <c r="L6" s="110" t="n"/>
-      <c r="M6" s="110" t="n"/>
-      <c r="N6" s="110" t="n"/>
-      <c r="O6" s="110" t="n"/>
-      <c r="P6" s="110" t="n"/>
-      <c r="Q6" s="111" t="n"/>
-      <c r="R6" s="101" t="n"/>
-      <c r="S6" s="110" t="n"/>
-      <c r="T6" s="110" t="n"/>
-      <c r="U6" s="110" t="n"/>
-      <c r="V6" s="110" t="n"/>
-      <c r="W6" s="110" t="n"/>
-      <c r="X6" s="110" t="n"/>
-      <c r="Y6" s="110" t="n"/>
-      <c r="Z6" s="110" t="n"/>
-      <c r="AA6" s="110" t="n"/>
-      <c r="AB6" s="110" t="n"/>
-      <c r="AC6" s="110" t="n"/>
-      <c r="AD6" s="110" t="n"/>
-      <c r="AE6" s="110" t="n"/>
-      <c r="AF6" s="110" t="n"/>
-      <c r="AG6" s="110" t="n"/>
-      <c r="AH6" s="110" t="n"/>
-      <c r="AI6" s="111" t="n"/>
-      <c r="AJ6" s="89" t="n"/>
-      <c r="AK6" s="110" t="n"/>
-      <c r="AL6" s="110" t="n"/>
-      <c r="AM6" s="110" t="n"/>
-      <c r="AN6" s="110" t="n"/>
-      <c r="AO6" s="110" t="n"/>
-      <c r="AP6" s="110" t="n"/>
-      <c r="AQ6" s="110" t="n"/>
-      <c r="AR6" s="111" t="n"/>
-      <c r="AS6" s="90" t="n"/>
+      <c r="B6" s="109" t="n"/>
+      <c r="C6" s="109" t="n"/>
+      <c r="D6" s="109" t="n"/>
+      <c r="E6" s="109" t="n"/>
+      <c r="F6" s="109" t="n"/>
+      <c r="G6" s="109" t="n"/>
+      <c r="H6" s="109" t="n"/>
+      <c r="I6" s="109" t="n"/>
+      <c r="J6" s="109" t="n"/>
+      <c r="K6" s="109" t="n"/>
+      <c r="L6" s="109" t="n"/>
+      <c r="M6" s="109" t="n"/>
+      <c r="N6" s="109" t="n"/>
+      <c r="O6" s="109" t="n"/>
+      <c r="P6" s="109" t="n"/>
+      <c r="Q6" s="109" t="n"/>
+      <c r="R6" s="109" t="n"/>
+      <c r="S6" s="109" t="n"/>
+      <c r="T6" s="109" t="n"/>
+      <c r="U6" s="109" t="n"/>
+      <c r="V6" s="109" t="n"/>
+      <c r="W6" s="109" t="n"/>
+      <c r="X6" s="109" t="n"/>
+      <c r="Y6" s="112" t="n"/>
+      <c r="Z6" s="101" t="n"/>
+      <c r="AA6" s="109" t="n"/>
+      <c r="AB6" s="109" t="n"/>
+      <c r="AC6" s="109" t="n"/>
+      <c r="AD6" s="109" t="n"/>
+      <c r="AE6" s="109" t="n"/>
+      <c r="AF6" s="109" t="n"/>
+      <c r="AG6" s="109" t="n"/>
+      <c r="AH6" s="109" t="n"/>
+      <c r="AI6" s="109" t="n"/>
+      <c r="AJ6" s="109" t="n"/>
+      <c r="AK6" s="109" t="n"/>
+      <c r="AL6" s="109" t="n"/>
+      <c r="AM6" s="109" t="n"/>
+      <c r="AN6" s="109" t="n"/>
+      <c r="AO6" s="109" t="n"/>
+      <c r="AP6" s="109" t="n"/>
+      <c r="AQ6" s="112" t="n"/>
+      <c r="AR6" s="89" t="n"/>
+      <c r="AS6" s="110" t="n"/>
       <c r="AT6" s="110" t="n"/>
       <c r="AU6" s="110" t="n"/>
       <c r="AV6" s="110" t="n"/>
@@ -3438,51 +3436,12 @@
       <c r="DD6" s="111" t="n"/>
     </row>
     <row r="7" ht="24" customFormat="1" customHeight="1" s="21">
-      <c r="A7" s="101" t="n"/>
-      <c r="B7" s="110" t="n"/>
-      <c r="C7" s="110" t="n"/>
-      <c r="D7" s="110" t="n"/>
-      <c r="E7" s="110" t="n"/>
-      <c r="F7" s="110" t="n"/>
-      <c r="G7" s="110" t="n"/>
-      <c r="H7" s="110" t="n"/>
-      <c r="I7" s="110" t="n"/>
-      <c r="J7" s="110" t="n"/>
-      <c r="K7" s="110" t="n"/>
-      <c r="L7" s="110" t="n"/>
-      <c r="M7" s="110" t="n"/>
-      <c r="N7" s="110" t="n"/>
-      <c r="O7" s="110" t="n"/>
-      <c r="P7" s="110" t="n"/>
-      <c r="Q7" s="111" t="n"/>
-      <c r="R7" s="101" t="n"/>
-      <c r="S7" s="110" t="n"/>
-      <c r="T7" s="110" t="n"/>
-      <c r="U7" s="110" t="n"/>
-      <c r="V7" s="110" t="n"/>
-      <c r="W7" s="110" t="n"/>
-      <c r="X7" s="110" t="n"/>
-      <c r="Y7" s="110" t="n"/>
-      <c r="Z7" s="110" t="n"/>
-      <c r="AA7" s="110" t="n"/>
-      <c r="AB7" s="110" t="n"/>
-      <c r="AC7" s="110" t="n"/>
-      <c r="AD7" s="110" t="n"/>
-      <c r="AE7" s="110" t="n"/>
-      <c r="AF7" s="110" t="n"/>
-      <c r="AG7" s="110" t="n"/>
-      <c r="AH7" s="110" t="n"/>
-      <c r="AI7" s="111" t="n"/>
-      <c r="AJ7" s="89" t="n"/>
-      <c r="AK7" s="110" t="n"/>
-      <c r="AL7" s="110" t="n"/>
-      <c r="AM7" s="110" t="n"/>
-      <c r="AN7" s="110" t="n"/>
-      <c r="AO7" s="110" t="n"/>
-      <c r="AP7" s="110" t="n"/>
-      <c r="AQ7" s="110" t="n"/>
-      <c r="AR7" s="111" t="n"/>
-      <c r="AS7" s="90" t="n"/>
+      <c r="A7" s="115" t="n"/>
+      <c r="Y7" s="116" t="n"/>
+      <c r="Z7" s="115" t="n"/>
+      <c r="AQ7" s="116" t="n"/>
+      <c r="AR7" s="89" t="n"/>
+      <c r="AS7" s="110" t="n"/>
       <c r="AT7" s="110" t="n"/>
       <c r="AU7" s="110" t="n"/>
       <c r="AV7" s="110" t="n"/>
@@ -3547,279 +3506,168 @@
       <c r="DC7" s="110" t="n"/>
       <c r="DD7" s="111" t="n"/>
     </row>
-    <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="102" t="n"/>
-      <c r="B8" s="103" t="inlineStr">
-        <is>
-          <t>* - информация указывается только для дерматологических СИЗ</t>
-        </is>
-      </c>
-      <c r="C8" s="109" t="n"/>
-      <c r="D8" s="109" t="n"/>
-      <c r="E8" s="109" t="n"/>
-      <c r="F8" s="109" t="n"/>
-      <c r="G8" s="109" t="n"/>
-      <c r="H8" s="109" t="n"/>
-      <c r="I8" s="109" t="n"/>
-      <c r="J8" s="109" t="n"/>
-      <c r="K8" s="109" t="n"/>
-      <c r="L8" s="109" t="n"/>
-      <c r="M8" s="109" t="n"/>
-      <c r="N8" s="109" t="n"/>
-      <c r="O8" s="109" t="n"/>
-      <c r="P8" s="109" t="n"/>
-      <c r="Q8" s="109" t="n"/>
-      <c r="R8" s="109" t="n"/>
-      <c r="S8" s="109" t="n"/>
-      <c r="T8" s="109" t="n"/>
-      <c r="U8" s="109" t="n"/>
-      <c r="V8" s="109" t="n"/>
-      <c r="W8" s="109" t="n"/>
-      <c r="X8" s="109" t="n"/>
-      <c r="Y8" s="109" t="n"/>
-      <c r="Z8" s="109" t="n"/>
-      <c r="AA8" s="109" t="n"/>
-      <c r="AB8" s="109" t="n"/>
-      <c r="AC8" s="109" t="n"/>
-      <c r="AD8" s="109" t="n"/>
-      <c r="AE8" s="109" t="n"/>
-      <c r="AF8" s="109" t="n"/>
-      <c r="AG8" s="109" t="n"/>
-      <c r="AH8" s="109" t="n"/>
-      <c r="AI8" s="109" t="n"/>
-      <c r="AJ8" s="109" t="n"/>
-      <c r="AK8" s="109" t="n"/>
-      <c r="AL8" s="109" t="n"/>
-      <c r="AM8" s="109" t="n"/>
-      <c r="AN8" s="109" t="n"/>
-      <c r="AO8" s="109" t="n"/>
-      <c r="AP8" s="109" t="n"/>
-      <c r="AQ8" s="109" t="n"/>
-      <c r="AR8" s="109" t="n"/>
-      <c r="AS8" s="109" t="n"/>
-      <c r="AT8" s="109" t="n"/>
-      <c r="AU8" s="109" t="n"/>
-      <c r="AV8" s="109" t="n"/>
-      <c r="AW8" s="109" t="n"/>
-      <c r="AX8" s="109" t="n"/>
-      <c r="AY8" s="109" t="n"/>
-      <c r="AZ8" s="109" t="n"/>
-      <c r="BA8" s="109" t="n"/>
-      <c r="BB8" s="109" t="n"/>
-      <c r="BC8" s="109" t="n"/>
-      <c r="BD8" s="109" t="n"/>
-      <c r="BE8" s="109" t="n"/>
-      <c r="BF8" s="109" t="n"/>
-      <c r="BG8" s="109" t="n"/>
-      <c r="BH8" s="109" t="n"/>
-      <c r="BI8" s="109" t="n"/>
-      <c r="BJ8" s="109" t="n"/>
-      <c r="BK8" s="109" t="n"/>
-      <c r="BL8" s="109" t="n"/>
-      <c r="BM8" s="109" t="n"/>
-      <c r="BN8" s="109" t="n"/>
-      <c r="BO8" s="109" t="n"/>
-      <c r="BP8" s="109" t="n"/>
-      <c r="BQ8" s="109" t="n"/>
-      <c r="BR8" s="109" t="n"/>
-      <c r="BS8" s="109" t="n"/>
-      <c r="BT8" s="109" t="n"/>
-      <c r="BU8" s="109" t="n"/>
-      <c r="BV8" s="109" t="n"/>
-      <c r="BW8" s="109" t="n"/>
-      <c r="BX8" s="109" t="n"/>
-      <c r="BY8" s="109" t="n"/>
-      <c r="BZ8" s="109" t="n"/>
-      <c r="CA8" s="109" t="n"/>
-      <c r="CB8" s="109" t="n"/>
-      <c r="CC8" s="109" t="n"/>
-      <c r="CD8" s="109" t="n"/>
-      <c r="CE8" s="109" t="n"/>
-      <c r="CF8" s="109" t="n"/>
-      <c r="CG8" s="109" t="n"/>
-      <c r="CH8" s="109" t="n"/>
-      <c r="CI8" s="109" t="n"/>
-      <c r="CJ8" s="109" t="n"/>
-      <c r="CK8" s="109" t="n"/>
-      <c r="CL8" s="109" t="n"/>
-      <c r="CM8" s="109" t="n"/>
-      <c r="CN8" s="109" t="n"/>
-      <c r="CO8" s="109" t="n"/>
-      <c r="CP8" s="109" t="n"/>
-      <c r="CQ8" s="109" t="n"/>
-      <c r="CR8" s="109" t="n"/>
-      <c r="CS8" s="109" t="n"/>
-      <c r="CT8" s="109" t="n"/>
-      <c r="CU8" s="109" t="n"/>
-      <c r="CV8" s="109" t="n"/>
-      <c r="CW8" s="109" t="n"/>
-      <c r="CX8" s="109" t="n"/>
-      <c r="CY8" s="109" t="n"/>
-      <c r="CZ8" s="109" t="n"/>
-      <c r="DA8" s="109" t="n"/>
-      <c r="DB8" s="109" t="n"/>
-      <c r="DC8" s="109" t="n"/>
-      <c r="DD8" s="104" t="n"/>
-    </row>
-    <row r="9" ht="31.5" customHeight="1">
-      <c r="A9" s="105" t="n"/>
-      <c r="B9" s="106" t="inlineStr">
-        <is>
-          <t>**_-_информация указывается для всех СИЗ, кроме дерматологических СИЗ и СИЗ однократного применения</t>
-        </is>
-      </c>
-      <c r="C9" s="108" t="n"/>
-      <c r="D9" s="108" t="n"/>
-      <c r="E9" s="108" t="n"/>
-      <c r="F9" s="108" t="n"/>
-      <c r="G9" s="108" t="n"/>
-      <c r="H9" s="108" t="n"/>
-      <c r="I9" s="108" t="n"/>
-      <c r="J9" s="108" t="n"/>
-      <c r="K9" s="108" t="n"/>
-      <c r="L9" s="108" t="n"/>
-      <c r="M9" s="108" t="n"/>
-      <c r="N9" s="108" t="n"/>
-      <c r="O9" s="108" t="n"/>
-      <c r="P9" s="108" t="n"/>
-      <c r="Q9" s="108" t="n"/>
-      <c r="R9" s="108" t="n"/>
-      <c r="S9" s="108" t="n"/>
-      <c r="T9" s="108" t="n"/>
-      <c r="U9" s="108" t="n"/>
-      <c r="V9" s="108" t="n"/>
-      <c r="W9" s="108" t="n"/>
-      <c r="X9" s="108" t="n"/>
-      <c r="Y9" s="108" t="n"/>
-      <c r="Z9" s="108" t="n"/>
-      <c r="AA9" s="108" t="n"/>
-      <c r="AB9" s="108" t="n"/>
-      <c r="AC9" s="108" t="n"/>
-      <c r="AD9" s="108" t="n"/>
-      <c r="AE9" s="108" t="n"/>
-      <c r="AF9" s="108" t="n"/>
-      <c r="AG9" s="108" t="n"/>
-      <c r="AH9" s="108" t="n"/>
-      <c r="AI9" s="108" t="n"/>
-      <c r="AJ9" s="108" t="n"/>
-      <c r="AK9" s="108" t="n"/>
-      <c r="AL9" s="108" t="n"/>
-      <c r="AM9" s="108" t="n"/>
-      <c r="AN9" s="108" t="n"/>
-      <c r="AO9" s="108" t="n"/>
-      <c r="AP9" s="108" t="n"/>
-      <c r="AQ9" s="108" t="n"/>
-      <c r="AR9" s="108" t="n"/>
-      <c r="AS9" s="108" t="n"/>
-      <c r="AT9" s="108" t="n"/>
-      <c r="AU9" s="108" t="n"/>
-      <c r="AV9" s="108" t="n"/>
-      <c r="AW9" s="108" t="n"/>
-      <c r="AX9" s="108" t="n"/>
-      <c r="AY9" s="108" t="n"/>
-      <c r="AZ9" s="108" t="n"/>
-      <c r="BA9" s="108" t="n"/>
-      <c r="BB9" s="108" t="n"/>
-      <c r="BC9" s="108" t="n"/>
-      <c r="BD9" s="108" t="n"/>
-      <c r="BE9" s="108" t="n"/>
-      <c r="BF9" s="108" t="n"/>
-      <c r="BG9" s="108" t="n"/>
-      <c r="BH9" s="108" t="n"/>
-      <c r="BI9" s="108" t="n"/>
-      <c r="BJ9" s="108" t="n"/>
-      <c r="BK9" s="108" t="n"/>
-      <c r="BL9" s="108" t="n"/>
-      <c r="BM9" s="108" t="n"/>
-      <c r="BN9" s="108" t="n"/>
-      <c r="BO9" s="108" t="n"/>
-      <c r="BP9" s="108" t="n"/>
-      <c r="BQ9" s="108" t="n"/>
-      <c r="BR9" s="108" t="n"/>
-      <c r="BS9" s="108" t="n"/>
-      <c r="BT9" s="108" t="n"/>
-      <c r="BU9" s="108" t="n"/>
-      <c r="BV9" s="108" t="n"/>
-      <c r="BW9" s="108" t="n"/>
-      <c r="BX9" s="108" t="n"/>
-      <c r="BY9" s="108" t="n"/>
-      <c r="BZ9" s="108" t="n"/>
-      <c r="CA9" s="108" t="n"/>
-      <c r="CB9" s="108" t="n"/>
-      <c r="CC9" s="108" t="n"/>
-      <c r="CD9" s="108" t="n"/>
-      <c r="CE9" s="108" t="n"/>
-      <c r="CF9" s="108" t="n"/>
-      <c r="CG9" s="108" t="n"/>
-      <c r="CH9" s="108" t="n"/>
-      <c r="CI9" s="108" t="n"/>
-      <c r="CJ9" s="108" t="n"/>
-      <c r="CK9" s="108" t="n"/>
-      <c r="CL9" s="108" t="n"/>
-      <c r="CM9" s="108" t="n"/>
-      <c r="CN9" s="108" t="n"/>
-      <c r="CO9" s="108" t="n"/>
-      <c r="CP9" s="108" t="n"/>
-      <c r="CQ9" s="108" t="n"/>
-      <c r="CR9" s="108" t="n"/>
-      <c r="CS9" s="108" t="n"/>
-      <c r="CT9" s="108" t="n"/>
-      <c r="CU9" s="108" t="n"/>
-      <c r="CV9" s="108" t="n"/>
-      <c r="CW9" s="108" t="n"/>
-      <c r="CX9" s="108" t="n"/>
-      <c r="CY9" s="108" t="n"/>
-      <c r="CZ9" s="108" t="n"/>
-      <c r="DA9" s="108" t="n"/>
-      <c r="DB9" s="108" t="n"/>
-      <c r="DC9" s="108" t="n"/>
-      <c r="DD9" s="107" t="n"/>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="113" t="n"/>
+      <c r="B8" s="108" t="n"/>
+      <c r="C8" s="108" t="n"/>
+      <c r="D8" s="108" t="n"/>
+      <c r="E8" s="108" t="n"/>
+      <c r="F8" s="108" t="n"/>
+      <c r="G8" s="108" t="n"/>
+      <c r="H8" s="108" t="n"/>
+      <c r="I8" s="108" t="n"/>
+      <c r="J8" s="108" t="n"/>
+      <c r="K8" s="108" t="n"/>
+      <c r="L8" s="108" t="n"/>
+      <c r="M8" s="108" t="n"/>
+      <c r="N8" s="108" t="n"/>
+      <c r="O8" s="108" t="n"/>
+      <c r="P8" s="108" t="n"/>
+      <c r="Q8" s="108" t="n"/>
+      <c r="R8" s="108" t="n"/>
+      <c r="S8" s="108" t="n"/>
+      <c r="T8" s="108" t="n"/>
+      <c r="U8" s="108" t="n"/>
+      <c r="V8" s="108" t="n"/>
+      <c r="W8" s="108" t="n"/>
+      <c r="X8" s="108" t="n"/>
+      <c r="Y8" s="114" t="n"/>
+      <c r="Z8" s="113" t="n"/>
+      <c r="AA8" s="108" t="n"/>
+      <c r="AB8" s="108" t="n"/>
+      <c r="AC8" s="108" t="n"/>
+      <c r="AD8" s="108" t="n"/>
+      <c r="AE8" s="108" t="n"/>
+      <c r="AF8" s="108" t="n"/>
+      <c r="AG8" s="108" t="n"/>
+      <c r="AH8" s="108" t="n"/>
+      <c r="AI8" s="108" t="n"/>
+      <c r="AJ8" s="108" t="n"/>
+      <c r="AK8" s="108" t="n"/>
+      <c r="AL8" s="108" t="n"/>
+      <c r="AM8" s="108" t="n"/>
+      <c r="AN8" s="108" t="n"/>
+      <c r="AO8" s="108" t="n"/>
+      <c r="AP8" s="108" t="n"/>
+      <c r="AQ8" s="114" t="n"/>
+      <c r="AR8" s="89" t="n"/>
+      <c r="AS8" s="110" t="n"/>
+      <c r="AT8" s="110" t="n"/>
+      <c r="AU8" s="110" t="n"/>
+      <c r="AV8" s="110" t="n"/>
+      <c r="AW8" s="110" t="n"/>
+      <c r="AX8" s="110" t="n"/>
+      <c r="AY8" s="110" t="n"/>
+      <c r="AZ8" s="111" t="n"/>
+      <c r="BA8" s="90" t="n"/>
+      <c r="BB8" s="110" t="n"/>
+      <c r="BC8" s="110" t="n"/>
+      <c r="BD8" s="110" t="n"/>
+      <c r="BE8" s="110" t="n"/>
+      <c r="BF8" s="110" t="n"/>
+      <c r="BG8" s="110" t="n"/>
+      <c r="BH8" s="111" t="n"/>
+      <c r="BI8" s="90" t="n"/>
+      <c r="BJ8" s="110" t="n"/>
+      <c r="BK8" s="110" t="n"/>
+      <c r="BL8" s="110" t="n"/>
+      <c r="BM8" s="110" t="n"/>
+      <c r="BN8" s="110" t="n"/>
+      <c r="BO8" s="110" t="n"/>
+      <c r="BP8" s="110" t="n"/>
+      <c r="BQ8" s="110" t="n"/>
+      <c r="BR8" s="111" t="n"/>
+      <c r="BS8" s="89" t="n"/>
+      <c r="BT8" s="110" t="n"/>
+      <c r="BU8" s="110" t="n"/>
+      <c r="BV8" s="110" t="n"/>
+      <c r="BW8" s="110" t="n"/>
+      <c r="BX8" s="110" t="n"/>
+      <c r="BY8" s="110" t="n"/>
+      <c r="BZ8" s="110" t="n"/>
+      <c r="CA8" s="111" t="n"/>
+      <c r="CB8" s="90" t="n"/>
+      <c r="CC8" s="110" t="n"/>
+      <c r="CD8" s="110" t="n"/>
+      <c r="CE8" s="110" t="n"/>
+      <c r="CF8" s="110" t="n"/>
+      <c r="CG8" s="110" t="n"/>
+      <c r="CH8" s="110" t="n"/>
+      <c r="CI8" s="111" t="n"/>
+      <c r="CJ8" s="90" t="n"/>
+      <c r="CK8" s="110" t="n"/>
+      <c r="CL8" s="110" t="n"/>
+      <c r="CM8" s="110" t="n"/>
+      <c r="CN8" s="110" t="n"/>
+      <c r="CO8" s="110" t="n"/>
+      <c r="CP8" s="110" t="n"/>
+      <c r="CQ8" s="110" t="n"/>
+      <c r="CR8" s="110" t="n"/>
+      <c r="CS8" s="111" t="n"/>
+      <c r="CT8" s="89" t="n"/>
+      <c r="CU8" s="110" t="n"/>
+      <c r="CV8" s="110" t="n"/>
+      <c r="CW8" s="110" t="n"/>
+      <c r="CX8" s="110" t="n"/>
+      <c r="CY8" s="110" t="n"/>
+      <c r="CZ8" s="110" t="n"/>
+      <c r="DA8" s="110" t="n"/>
+      <c r="DB8" s="110" t="n"/>
+      <c r="DC8" s="110" t="n"/>
+      <c r="DD8" s="111" t="n"/>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="B9" s="117" t="inlineStr">
+        <is>
+          <t>** - информация указывается для всех СИЗ, кроме дерматологических СИЗ и СИЗ однократного применения</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="44">
     <mergeCell ref="BI6:BR6"/>
-    <mergeCell ref="AS5:AZ5"/>
-    <mergeCell ref="AJ7:AR7"/>
-    <mergeCell ref="R7:AI7"/>
-    <mergeCell ref="R3:AI4"/>
     <mergeCell ref="BI5:BR5"/>
-    <mergeCell ref="A3:Q4"/>
     <mergeCell ref="BS4:CA4"/>
-    <mergeCell ref="R6:AI6"/>
+    <mergeCell ref="A5:Y5"/>
     <mergeCell ref="BI4:BR4"/>
-    <mergeCell ref="A6:Q6"/>
+    <mergeCell ref="AR4:AZ4"/>
+    <mergeCell ref="BA8:BH8"/>
     <mergeCell ref="CT6:DD6"/>
-    <mergeCell ref="AS4:AZ4"/>
     <mergeCell ref="CJ7:CS7"/>
+    <mergeCell ref="B9:DD9"/>
+    <mergeCell ref="AR8:AZ8"/>
     <mergeCell ref="BS3:DD3"/>
-    <mergeCell ref="AJ6:AR6"/>
+    <mergeCell ref="AR6:AZ6"/>
+    <mergeCell ref="BA7:BH7"/>
     <mergeCell ref="CT5:DD5"/>
-    <mergeCell ref="BA7:BH7"/>
-    <mergeCell ref="A7:Q7"/>
-    <mergeCell ref="B8:DC8"/>
     <mergeCell ref="BS6:CA6"/>
+    <mergeCell ref="AR5:AZ5"/>
     <mergeCell ref="CB7:CI7"/>
-    <mergeCell ref="AJ5:AR5"/>
-    <mergeCell ref="AS6:AZ6"/>
-    <mergeCell ref="AJ4:AR4"/>
+    <mergeCell ref="Z5:AQ5"/>
+    <mergeCell ref="A3:Y4"/>
     <mergeCell ref="BS7:CA7"/>
-    <mergeCell ref="B9:DC9"/>
     <mergeCell ref="CJ5:CS5"/>
     <mergeCell ref="CT4:DD4"/>
+    <mergeCell ref="Z3:AQ4"/>
+    <mergeCell ref="BI8:BR8"/>
     <mergeCell ref="BA6:BH6"/>
-    <mergeCell ref="AS7:AZ7"/>
-    <mergeCell ref="R5:AI5"/>
+    <mergeCell ref="CB8:CI8"/>
+    <mergeCell ref="CJ8:CS8"/>
+    <mergeCell ref="CT7:DD7"/>
+    <mergeCell ref="BI7:BR7"/>
     <mergeCell ref="BA5:BH5"/>
-    <mergeCell ref="CT7:DD7"/>
-    <mergeCell ref="AJ3:BR3"/>
+    <mergeCell ref="AR7:AZ7"/>
     <mergeCell ref="CJ4:CS4"/>
-    <mergeCell ref="A5:Q5"/>
-    <mergeCell ref="BI7:BR7"/>
+    <mergeCell ref="AR3:BR3"/>
     <mergeCell ref="CB5:CI5"/>
+    <mergeCell ref="Z6:AQ8"/>
     <mergeCell ref="CB4:CI4"/>
     <mergeCell ref="BA4:BH4"/>
+    <mergeCell ref="A6:Y8"/>
+    <mergeCell ref="CT8:DD8"/>
     <mergeCell ref="BS5:CA5"/>
     <mergeCell ref="CB6:CI6"/>
+    <mergeCell ref="BS8:CA8"/>
     <mergeCell ref="CJ6:CS6"/>
   </mergeCells>
   <pageMargins left="0.3937007874015748" right="0.7086614173228347" top="0.5905511811023623" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>

--- a/templates/card_template.xlsx
+++ b/templates/card_template.xlsx
@@ -2903,7 +2903,7 @@
   <pageMargins left="0.7874015748031497" right="0.3149606299212598" top="0.5905511811023623" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter alignWithMargins="0">
-    <oddHeader>&amp;R&amp;"Times New Roman,обычный"&amp;7Подготовлено с использованием системы &amp;"Times New Roman,полужирный"КонсультантПлюс</oddHeader>
+    <oddHeader/>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -3673,7 +3673,7 @@
   <pageMargins left="0.3937007874015748" right="0.7086614173228347" top="0.5905511811023623" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter alignWithMargins="0">
-    <oddHeader>&amp;R&amp;"Times New Roman,обычный"&amp;7Подготовлено с использованием системы &amp;"Times New Roman,полужирный"КонсультантПлюс</oddHeader>
+    <oddHeader/>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
